--- a/stories/arbres/ATOM-REL.CON.002-08.xlsx
+++ b/stories/arbres/ATOM-REL.CON.002-08.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Étienne est dans la cour. Un camarade le bouscule. Étienne sent son épaule. Il dit : stop. Il fait un pas. Il s'éloigne. Il va vers la maîtresse. La maîtresse écoute. Plus tard, dans le préau, un camarade le bouscule encore. Étienne se souvient. Il dit : stop. Il s'éloigne. Il rejoint la maîtresse. Même leçon, autre lieu. Papa vient le soir. Étienne raconte. Papa dit : stop, s'éloigner, maîtresse.</t>
+          <t>Étienne est dans la cour. Un camarade le bouscule. Étienne sent son épaule. Stop. Il fait un pas. Il s'éloigne. Il va vers la maîtresse. La maîtresse écoute. Plus tard, dans le préau, un camarade le bouscule encore. Étienne se souvient. Stop. Il s'éloigne. Il rejoint la maîtresse. Même leçon, autre lieu. Papa vient le soir. Étienne raconte. Stop, s'éloigner, maîtresse.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,16 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Étienne est dans la cour. Un camarade le bouscule. Étienne sent son épaule.
+narrateur|Stop. Il fait un pas.
+narrateur|Il s'éloigne. Il va vers la maîtresse. La maîtresse écoute. Plus tard, dans le préau, un camarade le bouscule encore. Étienne se souvient.
+narrateur|Stop.
+narrateur|Il s'éloigne. Il rejoint la maîtresse. Même leçon, autre lieu. Papa vient le soir. Étienne raconte.
+papa|Stop, s'éloigner, maîtresse.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1465,6 +1491,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Un camarade bouscule Étienne. Que fait-il ?</t>
         </is>
       </c>
     </row>
@@ -1633,6 +1664,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Étienne a dit stop. Il s'est éloigné. Il a rejoint la maîtresse. Papa a écouté le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1791,6 +1827,11 @@
         <v>8</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Étienne range son cartable. Papa marche à côté.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1953,6 +1994,11 @@
         <v>8</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1971,7 +2017,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1988,6 +2034,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-REL.CON.002-08.xlsx
+++ b/stories/arbres/ATOM-REL.CON.002-08.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1315,6 +1320,7 @@
 papa|Stop, s'éloigner, maîtresse.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1498,6 +1504,7 @@
           <t>narrateur|Un camarade bouscule Étienne. Que fait-il ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1669,6 +1676,7 @@
           <t>narrateur|Étienne a dit stop. Il s'est éloigné. Il a rejoint la maîtresse. Papa a écouté le soir.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1832,6 +1840,7 @@
           <t>narrateur|Étienne range son cartable. Papa marche à côté.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1999,6 +2008,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2017,7 +2027,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2041,6 +2051,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2055,7 +2079,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2242,6 +2266,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-REL.CON.002-08.xlsx
+++ b/stories/arbres/ATOM-REL.CON.002-08.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Étienne dit stop et rejoint la maîtresse</t>
+          <t>Amir dit stop et rejoint la maîtresse</t>
         </is>
       </c>
     </row>
@@ -830,6 +830,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Amir joue dans la cour, puis sous le préau. Un camarade passe trop près, deux fois. Amir dit stop, s'éloigne, rejoint la maîtresse.</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1184,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Étienne est dans la cour. Un camarade le bouscule. Étienne sent son épaule. Stop. Il fait un pas. Il s'éloigne. Il va vers la maîtresse. La maîtresse écoute. Plus tard, dans le préau, un camarade le bouscule encore. Étienne se souvient. Stop. Il s'éloigne. Il rejoint la maîtresse. Même leçon, autre lieu. Papa vient le soir. Étienne raconte. Stop, s'éloigner, maîtresse.</t>
+          <t>Un bateau de papier tourne dans une flaque. Le pli blanc est un peu mouillé. Un coin du bateau s'ouvre, tout doux. L'ombre du préau commence au bord de l'eau. Une pierre plate tient le soleil. Papa pose le cartable près du grillage. Tu as vu le bateau, Amir ? Oui, papa. Il tourne tout seul. La flaque le pousse. Je reviens ce soir. D'accord. En ce moment, Amir est dans la cour. Le soleil chauffe une pierre plate. Amir s'accroupit près de la flaque. Le bateau tourne encore. Un pli du papier se mouille plus. Un camarade passe trop près. Amir sent son épaule. Son cœur tape. Stop. Amir fait un pas. Il peut s'éloigner. S'éloigner, c'est aller vers la maîtresse. Amir marche vers elle. On m'a bousculé. La maîtresse l'écoute. Amir reste près d'elle. Plus tard, sous le préau, le camarade passe trop près encore. Amir se souvient. Stop. Il s'éloigne. Il rejoint la maîtresse. Même chose. La maîtresse l'écoute encore. Amir reste près d'elle. Il pose une main sur le pilier du préau. Le pilier est froid et un peu rugueux. Je reste ici. Amir souffle. Son cœur tape moins vite. Le bateau de papier a arrêté de tourner. Papa vient le soir. La pierre plate n'est plus chaude. Amir la touche du bout du doigt. Elle est juste tiède. Tu as vu le bateau, encore ? Il ne tourne plus. Dans la cour, trop près. Puis sous le préau. J'ai dit stop. Je suis allé vers la maîtresse. Bravo, Amir. Tu as dit stop. Tu t'es éloigné. Tu as rejoint la maîtresse. C'est du bon travail. Même sous le préau ? Oui. Même leçon, autre lieu. Oui, papa. Papa prend sa main. Le bateau de papier reste dans l'herbe, tout mou.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1312,12 +1324,69 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Étienne est dans la cour. Un camarade le bouscule. Étienne sent son épaule.
-narrateur|Stop. Il fait un pas.
-narrateur|Il s'éloigne. Il va vers la maîtresse. La maîtresse écoute. Plus tard, dans le préau, un camarade le bouscule encore. Étienne se souvient.
-narrateur|Stop.
-narrateur|Il s'éloigne. Il rejoint la maîtresse. Même leçon, autre lieu. Papa vient le soir. Étienne raconte.
-papa|Stop, s'éloigner, maîtresse.</t>
+          <t>narrateur|Un bateau de papier tourne dans une flaque.
+narrateur|Le pli blanc est un peu mouillé.
+narrateur|Un coin du bateau s'ouvre, tout doux.
+narrateur|L'ombre du préau commence au bord de l'eau.
+narrateur|Une pierre plate tient le soleil.
+narrateur|Papa pose le cartable près du grillage.
+papa|Tu as vu le bateau, Amir ?
+enfant-m|Oui, papa.
+enfant-m|Il tourne tout seul.
+papa|La flaque le pousse.
+papa|Je reviens ce soir.
+enfant-m|D'accord.
+narrateur|En ce moment, Amir est dans la cour.
+narrateur|Le soleil chauffe une pierre plate.
+narrateur|Amir s'accroupit près de la flaque.
+enfant-m|Le bateau tourne encore.
+narrateur|Un pli du papier se mouille plus.
+narrateur|Un camarade passe trop près.
+narrateur|Amir sent son épaule.
+narrateur|Son cœur tape.
+enfant-m|Stop.
+narrateur|Amir fait un pas.
+narrateur|Il peut s'éloigner.
+narrateur|S'éloigner, c'est aller vers la maîtresse.
+narrateur|Amir marche vers elle.
+enfant-m|On m'a bousculé.
+narrateur|La maîtresse l'écoute.
+narrateur|Amir reste près d'elle.
+narrateur|Plus tard, sous le préau, le camarade passe trop près encore.
+narrateur|Amir se souvient.
+enfant-m|Stop.
+narrateur|Il s'éloigne.
+narrateur|Il rejoint la maîtresse.
+enfant-m|Même chose.
+narrateur|La maîtresse l'écoute encore.
+narrateur|Amir reste près d'elle.
+narrateur|Il pose une main sur le pilier du préau.
+narrateur|Le pilier est froid et un peu rugueux.
+enfant-m|Je reste ici.
+narrateur|Amir souffle.
+narrateur|Son cœur tape moins vite.
+narrateur|Le bateau de papier a arrêté de tourner.
+narrateur|Papa vient le soir.
+narrateur|La pierre plate n'est plus chaude.
+narrateur|Amir la touche du bout du doigt.
+narrateur|Elle est juste tiède.
+papa|Tu as vu le bateau, encore ?
+enfant-m|Il ne tourne plus.
+enfant-m|Dans la cour, trop près.
+enfant-m|Puis sous le préau.
+enfant-m|J'ai dit stop.
+enfant-m|Je suis allé vers la maîtresse.
+papa|Bravo, Amir.
+papa|Tu as dit stop.
+papa|Tu t'es éloigné.
+papa|Tu as rejoint la maîtresse.
+papa|C'est du bon travail.
+papa|Même sous le préau ?
+enfant-m|Oui.
+papa|Même leçon, autre lieu.
+enfant-m|Oui, papa.
+narrateur|Papa prend sa main.
+narrateur|Le bateau de papier reste dans l'herbe, tout mou.</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr"/>
@@ -1345,7 +1414,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Un camarade bouscule Étienne. Que fait-il ?</t>
+          <t>Un camarade bouscule Amir. Que fait-il ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -1501,7 +1570,8 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Un camarade bouscule Étienne. Que fait-il ?</t>
+          <t>narrateur|Un camarade bouscule Amir.
+narrateur|Que fait-il ?</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr"/>
@@ -1529,7 +1599,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Étienne a dit stop. Il s'est éloigné. Il a rejoint la maîtresse. Papa a écouté le soir.</t>
+          <t>Amir a dit stop. Il s'est éloigné. Il a rejoint la maîtresse. Bravo. Dans la cour, et sous le préau. Stop, puis la maîtresse. Oui. Tu as fait du bon travail.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1673,7 +1743,14 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Étienne a dit stop. Il s'est éloigné. Il a rejoint la maîtresse. Papa a écouté le soir.</t>
+          <t>narrateur|Amir a dit stop.
+narrateur|Il s'est éloigné.
+narrateur|Il a rejoint la maîtresse.
+papa|Bravo.
+papa|Dans la cour, et sous le préau.
+enfant-m|Stop, puis la maîtresse.
+papa|Oui.
+papa|Tu as fait du bon travail.</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr"/>
@@ -1701,7 +1778,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Étienne range son cartable. Papa marche à côté.</t>
+          <t>Amir range son cartable. Je marche à côté. Oui, papa. On laisse le bateau dans l'herbe ? Oui. Il est trop mou, maintenant. Oui, papa. La flaque ne pousse plus rien. L'ombre du préau a grandi. La pierre est tiède, encore ? Juste un peu. Le pli du bateau reste ouvert.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1837,7 +1914,18 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Étienne range son cartable. Papa marche à côté.</t>
+          <t>narrateur|Amir range son cartable.
+papa|Je marche à côté.
+enfant-m|Oui, papa.
+papa|On laisse le bateau dans l'herbe ?
+enfant-m|Oui.
+papa|Il est trop mou, maintenant.
+enfant-m|Oui, papa.
+narrateur|La flaque ne pousse plus rien.
+narrateur|L'ombre du préau a grandi.
+papa|La pierre est tiède, encore ?
+enfant-m|Juste un peu.
+narrateur|Le pli du bateau reste ouvert.</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr"/>
@@ -1865,7 +1953,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'ai dit stop. Je suis allé vers la maîtresse. Bravo, Amir. Tu as fait du bon travail. Le bateau de papier sèche tout bas. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2005,7 +2093,12 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|J'ai dit stop.
+enfant-m|Je suis allé vers la maîtresse.
+papa|Bravo, Amir.
+papa|Tu as fait du bon travail.
+narrateur|Le bateau de papier sèche tout bas.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr"/>
@@ -2027,7 +2120,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2065,6 +2158,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-REL.CON.002-08.xlsx
+++ b/stories/arbres/ATOM-REL.CON.002-08.xlsx
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Un bateau de papier tourne dans une flaque. Le pli blanc est un peu mouillé. Un coin du bateau s'ouvre, tout doux. L'ombre du préau commence au bord de l'eau. Une pierre plate tient le soleil. Papa pose le cartable près du grillage. Tu as vu le bateau, Amir ? Oui, papa. Il tourne tout seul. La flaque le pousse. Je reviens ce soir. D'accord. En ce moment, Amir est dans la cour. Le soleil chauffe une pierre plate. Amir s'accroupit près de la flaque. Le bateau tourne encore. Un pli du papier se mouille plus. Un camarade passe trop près. Amir sent son épaule. Son cœur tape. Stop. Amir fait un pas. Il peut s'éloigner. S'éloigner, c'est aller vers la maîtresse. Amir marche vers elle. On m'a bousculé. La maîtresse l'écoute. Amir reste près d'elle. Plus tard, sous le préau, le camarade passe trop près encore. Amir se souvient. Stop. Il s'éloigne. Il rejoint la maîtresse. Même chose. La maîtresse l'écoute encore. Amir reste près d'elle. Il pose une main sur le pilier du préau. Le pilier est froid et un peu rugueux. Je reste ici. Amir souffle. Son cœur tape moins vite. Le bateau de papier a arrêté de tourner. Papa vient le soir. La pierre plate n'est plus chaude. Amir la touche du bout du doigt. Elle est juste tiède. Tu as vu le bateau, encore ? Il ne tourne plus. Dans la cour, trop près. Puis sous le préau. J'ai dit stop. Je suis allé vers la maîtresse. Bravo, Amir. Tu as dit stop. Tu t'es éloigné. Tu as rejoint la maîtresse. C'est du bon travail. Même sous le préau ? Oui. Même leçon, autre lieu. Oui, papa. Papa prend sa main. Le bateau de papier reste dans l'herbe, tout mou.</t>
+          <t>Un bateau de papier tourne dans une flaque. Le pli blanc est un peu mouillé. Un coin du bateau s'ouvre, tout doux. L'ombre du préau commence au bord de l'eau. Une pierre plate tient le soleil. Papa pose le cartable près du grillage. Tu as vu le bateau, Amir ? Oui, papa. Il tourne tout seul. La flaque le pousse. Je reviens ce soir. D'accord. En ce moment, Amir est dans la cour. Le soleil chauffe une pierre plate. Amir s'accroupit près de la flaque. Le bateau tourne encore. Un pli du papier se mouille plus. Un camarade passe trop près. Amir sent son épaule. Son cœur tape. Stop. Amir fait un pas. Il peut s'éloigner. S'éloigner, c'est aller vers la maîtresse. Amir marche vers elle. On m'a bousculé. La maîtresse l'écoute. Amir reste près d'elle. Plus tard, sous le préau, le camarade passe trop près encore. Amir se souvient. Stop. Il s'éloigne. Il rejoint la maîtresse. Même chose. La maîtresse l'écoute encore. Amir reste près d'elle. Il pose une main sur le pilier du préau. Le pilier est froid et un peu rugueux. Je reste ici. Amir souffle. Son cœur tape moins vite. Le bateau de papier a arrêté de tourner. Papa vient le soir. La pierre plate n'est plus chaude. Amir la touche du bout du doigt. Elle est juste tiède. Tu as vu le bateau, encore ? Il ne tourne plus. Dans la cour, trop près. Puis sous le préau. J'ai dit stop. Je suis allé vers la maîtresse. Bravo, Amir. Tu as dit stop. Tu t'es éloigné. Tu as rejoint la maîtresse. Même sous le préau ? Oui. Même leçon, autre lieu. Oui, papa. Papa prend sa main. Le bateau de papier reste dans l'herbe, tout mou.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Étienne est dans la cour. Un camarade le bouscule. Étienne sent son épaule. Il dit : &lt;emphasis level="moderate"&gt;stop&lt;/emphasis&gt;. Il fait un pas. Il s'éloigne. Il va vers la maîtresse. La maîtresse écoute. Plus tard, dans le préau, un camarade le bouscule encore. Étienne se souvient. Il dit : stop. Il s'éloigne. Il rejoint la maîtresse. Même leçon, autre lieu. Papa vient le soir. Étienne raconte. Papa dit : stop, s'éloigner, maîtresse.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>Un bateau de papier tourne dans une flaque. Le pli blanc est un peu mouillé. Un coin du bateau s'ouvre, tout doux. L'ombre du préau commence au bord de l'eau. Une pierre plate tient le soleil. Papa pose le cartable près du grillage. Tu as vu le bateau, Amir ? Oui, papa. Il tourne tout seul. La flaque le pousse. Je reviens ce soir. D'accord. En ce moment, Amir est dans la cour. Le soleil chauffe une pierre plate. Amir s'accroupit près de la flaque. Le bateau tourne encore. Un pli du papier se mouille plus. Un camarade passe trop près. Amir sent son épaule. Son cœur tape. Stop. Amir fait un pas. Il peut s'éloigner. S'éloigner, c'est aller vers la maîtresse. Amir marche vers elle. On m'a bousculé. La maîtresse l'écoute. Amir reste près d'elle. Plus tard, sous le préau, le camarade passe trop près encore. Amir se souvient. Stop. Il s'éloigne. Il rejoint la maîtresse. Même chose. La maîtresse l'écoute encore. Amir reste près d'elle. Il pose une main sur le pilier du préau. Le pilier est froid et un peu rugueux. Je reste ici. Amir souffle. Son cœur tape moins vite. Le bateau de papier a arrêté de tourner. Papa vient le soir. La pierre plate n'est plus chaude. Amir la touche du bout du doigt. Elle est juste tiède. Tu as vu le bateau, encore ? Il ne tourne plus. Dans la cour, trop près. Puis sous le préau. J'ai dit stop. Je suis allé vers la maîtresse. Bravo, Amir. Tu as dit stop. Tu t'es éloigné. Tu as rejoint la maîtresse. Même sous le préau ? Oui. Même leçon, autre lieu. Oui, papa. Papa prend sa main. Le bateau de papier reste dans l'herbe, tout mou.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1380,7 +1380,6 @@
 papa|Tu as dit stop.
 papa|Tu t'es éloigné.
 papa|Tu as rejoint la maîtresse.
-papa|C'est du bon travail.
 papa|Même sous le préau ?
 enfant-m|Oui.
 papa|Même leçon, autre lieu.
@@ -1389,7 +1388,6 @@
 narrateur|Le bateau de papier reste dans l'herbe, tout mou.</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1419,7 +1417,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Un camarade bouscule Étienne. Que fait-il ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>Un camarade bouscule Amir. Que fait-il ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1574,7 +1572,6 @@
 narrateur|Que fait-il ?</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1599,12 +1596,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Amir a dit stop. Il s'est éloigné. Il a rejoint la maîtresse. Bravo. Dans la cour, et sous le préau. Stop, puis la maîtresse. Oui. Tu as fait du bon travail.</t>
+          <t>Amir a dit stop. Il s'est éloigné. Il a rejoint la maîtresse. Bravo. Dans la cour, et sous le préau. Stop, puis la maîtresse. Oui.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Étienne a dit &lt;emphasis level="moderate"&gt;stop&lt;/emphasis&gt;. Il s'est éloigné. Il a rejoint la maîtresse. Papa a écouté le soir.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Amir a dit stop. Il s'est éloigné. Il a rejoint la maîtresse. Bravo. Dans la cour, et sous le préau. Stop, puis la maîtresse. Oui.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1749,11 +1746,9 @@
 papa|Bravo.
 papa|Dans la cour, et sous le préau.
 enfant-m|Stop, puis la maîtresse.
-papa|Oui.
-papa|Tu as fait du bon travail.</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr"/>
+papa|Oui.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1783,7 +1778,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Étienne range son cartable. Papa marche à côté.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Amir range son cartable. Je marche à côté. Oui, papa. On laisse le bateau dans l'herbe ? Oui. Il est trop mou, maintenant. Oui, papa. La flaque ne pousse plus rien. L'ombre du préau a grandi. La pierre est tiède, encore ? Juste un peu. Le pli du bateau reste ouvert.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1928,7 +1923,6 @@
 narrateur|Le pli du bateau reste ouvert.</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1953,12 +1947,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>J'ai dit stop. Je suis allé vers la maîtresse. Bravo, Amir. Tu as fait du bon travail. Le bateau de papier sèche tout bas. L'histoire est finie.</t>
+          <t>J'ai dit stop. Je suis allé vers la maîtresse. Bravo, Amir. Le bateau de papier sèche tout bas.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>J'ai dit stop. Je suis allé vers la maîtresse. Bravo, Amir. Le bateau de papier sèche tout bas.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2096,12 +2090,9 @@
           <t>enfant-m|J'ai dit stop.
 enfant-m|Je suis allé vers la maîtresse.
 papa|Bravo, Amir.
-papa|Tu as fait du bon travail.
-narrateur|Le bateau de papier sèche tout bas.
-narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+narrateur|Le bateau de papier sèche tout bas.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2120,7 +2111,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2165,6 +2156,13 @@
       <c r="A6" t="inlineStr">
         <is>
           <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-REL.CON.002-08.xlsx
+++ b/stories/arbres/ATOM-REL.CON.002-08.xlsx
@@ -683,7 +683,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Étienne, maîtresse, papa</t>
+          <t>Amir, maîtresse, papa</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-REL.CON.002-08.xlsx
+++ b/stories/arbres/ATOM-REL.CON.002-08.xlsx
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Amir dit stop et rejoint la maîtresse</t>
+          <t>Le bateau dans la flaque</t>
         </is>
       </c>
     </row>
@@ -671,7 +671,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>école, cour et préau</t>
+          <t>cour, flaque, préau, pierre plate</t>
         </is>
       </c>
     </row>
@@ -683,7 +683,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Amir, maîtresse, papa</t>
+          <t>Amir, Nino, papa</t>
         </is>
       </c>
     </row>
@@ -841,7 +841,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Amir joue dans la cour, puis sous le préau. Un camarade passe trop près, deux fois. Amir dit stop, s'éloigne, rejoint la maîtresse.</t>
+          <t>Amir veut que le bateau de papier traverse la flaque. Nino passe trop près. Stop, maîtresse. Sous le préau, il veut sécher un pli sur la pierre. Nino trop près encore. Stop. Le bateau reste mou dans l'herbe.</t>
         </is>
       </c>
     </row>
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Un bateau de papier tourne dans une flaque. Le pli blanc est un peu mouillé. Un coin du bateau s'ouvre, tout doux. L'ombre du préau commence au bord de l'eau. Une pierre plate tient le soleil. Papa pose le cartable près du grillage. Tu as vu le bateau, Amir ? Oui, papa. Il tourne tout seul. La flaque le pousse. Je reviens ce soir. D'accord. En ce moment, Amir est dans la cour. Le soleil chauffe une pierre plate. Amir s'accroupit près de la flaque. Le bateau tourne encore. Un pli du papier se mouille plus. Un camarade passe trop près. Amir sent son épaule. Son cœur tape. Stop. Amir fait un pas. Il peut s'éloigner. S'éloigner, c'est aller vers la maîtresse. Amir marche vers elle. On m'a bousculé. La maîtresse l'écoute. Amir reste près d'elle. Plus tard, sous le préau, le camarade passe trop près encore. Amir se souvient. Stop. Il s'éloigne. Il rejoint la maîtresse. Même chose. La maîtresse l'écoute encore. Amir reste près d'elle. Il pose une main sur le pilier du préau. Le pilier est froid et un peu rugueux. Je reste ici. Amir souffle. Son cœur tape moins vite. Le bateau de papier a arrêté de tourner. Papa vient le soir. La pierre plate n'est plus chaude. Amir la touche du bout du doigt. Elle est juste tiède. Tu as vu le bateau, encore ? Il ne tourne plus. Dans la cour, trop près. Puis sous le préau. J'ai dit stop. Je suis allé vers la maîtresse. Bravo, Amir. Tu as dit stop. Tu t'es éloigné. Tu as rejoint la maîtresse. Même sous le préau ? Oui. Même leçon, autre lieu. Oui, papa. Papa prend sa main. Le bateau de papier reste dans l'herbe, tout mou.</t>
+          <t>Un bateau de papier penche dans l'eau grise. Le pli blanc est un peu mouillé. Un coin du bateau s'ouvre, tout doux. L'ombre du préau commence au bord de l'eau. Une pierre plate tient le soleil. Papa pose le cartable près du grillage. Tu as vu le bateau, Amir ? Oui, papa. Il penche tout seul. La flaque le pousse. Je reviens ce soir. D'accord. Papa part le long du grillage. En ce moment, Amir s'accroupit près de la flaque. L'eau est froide sous un doigt. Je veux qu'il aille de l'autre côté. Il souffle tout doux vers le pli. Le bateau avance d'un tout petit bout. Encore. Nino arrive très vite. Nino passe trop près de l'épaule. Le bateau se renverse un peu. Amir sent le choc. Son cœur tape. Stop. Il fait un pas vers le préau. Ses chaussures clapotent au bord. Il marche jusqu'à la maîtresse. Nino est passé trop près. La maîtresse l'écoute. Amir reste près d'elle. Il pose une main sur le pilier. Le pilier est froid et un peu rugueux. Je reste ici. Le bateau attend dans l'eau, tout mou. Amir souffle. Son cœur tape moins vite. Plus tard, l'ombre du préau a grandi. Amir ramasse le bateau. Le papier colle à ses doigts. Je veux sécher le pli, sur la pierre. La pierre plate est encore un peu chaude. Il pose le bateau dessus. Un coin se redresse, tout lentement. Nino passe trop près encore. Le bateau glisse vers le bord. Amir sent son épaule. Stop. Il fait un pas. La maîtresse est sous le préau, maintenant. Amir marche vers elle. La pierre reste derrière. Encore trop près. La maîtresse l'écoute encore. Amir reste près d'elle. Il pose une main sur le pilier du préau. Le ciment est froid. Je reste ici. Il souffle. Le bateau a arrêté de tourner. Papa vient le soir. La pierre plate n'est plus chaude. Amir la touche du bout du doigt. Elle est juste tiède. Tu as vu le bateau, encore ? Il ne tourne plus. Dans la flaque, trop près. Puis sur la pierre. J'ai dit stop. Je suis allé vers la maîtresse. Près de l'eau ? Oui. Et sous le préau ? Stop encore. Bravo, Amir. Tu es allé près d'elle. Oui, papa. Papa prend sa main. Le bateau de papier reste dans l'herbe, tout mou.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Un bateau de papier tourne dans une flaque. Le pli blanc est un peu mouillé. Un coin du bateau s'ouvre, tout doux. L'ombre du préau commence au bord de l'eau. Une pierre plate tient le soleil. Papa pose le cartable près du grillage. Tu as vu le bateau, Amir ? Oui, papa. Il tourne tout seul. La flaque le pousse. Je reviens ce soir. D'accord. En ce moment, Amir est dans la cour. Le soleil chauffe une pierre plate. Amir s'accroupit près de la flaque. Le bateau tourne encore. Un pli du papier se mouille plus. Un camarade passe trop près. Amir sent son épaule. Son cœur tape. Stop. Amir fait un pas. Il peut s'éloigner. S'éloigner, c'est aller vers la maîtresse. Amir marche vers elle. On m'a bousculé. La maîtresse l'écoute. Amir reste près d'elle. Plus tard, sous le préau, le camarade passe trop près encore. Amir se souvient. Stop. Il s'éloigne. Il rejoint la maîtresse. Même chose. La maîtresse l'écoute encore. Amir reste près d'elle. Il pose une main sur le pilier du préau. Le pilier est froid et un peu rugueux. Je reste ici. Amir souffle. Son cœur tape moins vite. Le bateau de papier a arrêté de tourner. Papa vient le soir. La pierre plate n'est plus chaude. Amir la touche du bout du doigt. Elle est juste tiède. Tu as vu le bateau, encore ? Il ne tourne plus. Dans la cour, trop près. Puis sous le préau. J'ai dit stop. Je suis allé vers la maîtresse. Bravo, Amir. Tu as dit stop. Tu t'es éloigné. Tu as rejoint la maîtresse. Même sous le préau ? Oui. Même leçon, autre lieu. Oui, papa. Papa prend sa main. Le bateau de papier reste dans l'herbe, tout mou.</t>
+          <t>Un bateau de papier penche dans l'eau grise. Le pli blanc est un peu mouillé. Un coin du bateau s'ouvre, tout doux. L'ombre du préau commence au bord de l'eau. Une pierre plate tient le soleil. Papa pose le cartable près du grillage. Tu as vu le bateau, Amir ? Oui, papa. Il penche tout seul. La flaque le pousse. Je reviens ce soir. D'accord. Papa part le long du grillage. En ce moment, Amir s'accroupit près de la flaque. L'eau est froide sous un doigt. Je veux qu'il aille de l'autre côté. Il souffle tout doux vers le pli. Le bateau avance d'un tout petit bout. Encore. Nino arrive très vite. Nino passe trop près de l'épaule. Le bateau se renverse un peu. Amir sent le choc. Son cœur tape. Stop. Il fait un pas vers le préau. Ses chaussures clapotent au bord. Il marche jusqu'à la maîtresse. Nino est passé trop près. La maîtresse l'écoute. Amir reste près d'elle. Il pose une main sur le pilier. Le pilier est froid et un peu rugueux. Je reste ici. Le bateau attend dans l'eau, tout mou. Amir souffle. Son cœur tape moins vite. Plus tard, l'ombre du préau a grandi. Amir ramasse le bateau. Le papier colle à ses doigts. Je veux sécher le pli, sur la pierre. La pierre plate est encore un peu chaude. Il pose le bateau dessus. Un coin se redresse, tout lentement. Nino passe trop près encore. Le bateau glisse vers le bord. Amir sent son épaule. Stop. Il fait un pas. La maîtresse est sous le préau, maintenant. Amir marche vers elle. La pierre reste derrière. Encore trop près. La maîtresse l'écoute encore. Amir reste près d'elle. Il pose une main sur le pilier du préau. Le ciment est froid. Je reste ici. Il souffle. Le bateau a arrêté de tourner. Papa vient le soir. La pierre plate n'est plus chaude. Amir la touche du bout du doigt. Elle est juste tiède. Tu as vu le bateau, encore ? Il ne tourne plus. Dans la flaque, trop près. Puis sur la pierre. J'ai dit stop. Je suis allé vers la maîtresse. Près de l'eau ? Oui. Et sous le préau ? Stop encore. Bravo, Amir. Tu es allé près d'elle. Oui, papa. Papa prend sa main. Le bateau de papier reste dans l'herbe, tout mou.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1252,7 +1252,7 @@
         <v>0.96</v>
       </c>
       <c r="AB2" s="2" t="n">
-        <v>1.12</v>
+        <v>1.22</v>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
@@ -1324,7 +1324,7 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Un bateau de papier tourne dans une flaque.
+          <t>narrateur|Un bateau de papier penche dans l'eau grise.
 narrateur|Le pli blanc est un peu mouillé.
 narrateur|Un coin du bateau s'ouvre, tout doux.
 narrateur|L'ombre du préau commence au bord de l'eau.
@@ -1332,57 +1332,74 @@
 narrateur|Papa pose le cartable près du grillage.
 papa|Tu as vu le bateau, Amir ?
 enfant-m|Oui, papa.
-enfant-m|Il tourne tout seul.
+enfant-m|Il penche tout seul.
 papa|La flaque le pousse.
 papa|Je reviens ce soir.
 enfant-m|D'accord.
-narrateur|En ce moment, Amir est dans la cour.
-narrateur|Le soleil chauffe une pierre plate.
-narrateur|Amir s'accroupit près de la flaque.
-enfant-m|Le bateau tourne encore.
-narrateur|Un pli du papier se mouille plus.
-narrateur|Un camarade passe trop près.
-narrateur|Amir sent son épaule.
+narrateur|Papa part le long du grillage.
+narrateur|En ce moment, Amir s'accroupit près de la flaque.
+narrateur|L'eau est froide sous un doigt.
+enfant-m|Je veux qu'il aille de l'autre côté.
+narrateur|Il souffle tout doux vers le pli.
+narrateur|Le bateau avance d'un tout petit bout.
+enfant-m|Encore.
+narrateur|Nino arrive très vite.
+narrateur|Nino passe trop près de l'épaule.
+narrateur|Le bateau se renverse un peu.
+narrateur|Amir sent le choc.
 narrateur|Son cœur tape.
 enfant-m|Stop.
-narrateur|Amir fait un pas.
-narrateur|Il peut s'éloigner.
-narrateur|S'éloigner, c'est aller vers la maîtresse.
-narrateur|Amir marche vers elle.
-enfant-m|On m'a bousculé.
+narrateur|Il fait un pas vers le préau.
+narrateur|Ses chaussures clapotent au bord.
+narrateur|Il marche jusqu'à la maîtresse.
+enfant-m|Nino est passé trop près.
 narrateur|La maîtresse l'écoute.
 narrateur|Amir reste près d'elle.
-narrateur|Plus tard, sous le préau, le camarade passe trop près encore.
-narrateur|Amir se souvient.
+narrateur|Il pose une main sur le pilier.
+narrateur|Le pilier est froid et un peu rugueux.
+enfant-m|Je reste ici.
+narrateur|Le bateau attend dans l'eau, tout mou.
+narrateur|Amir souffle.
+narrateur|Son cœur tape moins vite.
+narrateur|Plus tard, l'ombre du préau a grandi.
+narrateur|Amir ramasse le bateau.
+narrateur|Le papier colle à ses doigts.
+enfant-m|Je veux sécher le pli, sur la pierre.
+narrateur|La pierre plate est encore un peu chaude.
+narrateur|Il pose le bateau dessus.
+narrateur|Un coin se redresse, tout lentement.
+narrateur|Nino passe trop près encore.
+narrateur|Le bateau glisse vers le bord.
+narrateur|Amir sent son épaule.
 enfant-m|Stop.
-narrateur|Il s'éloigne.
-narrateur|Il rejoint la maîtresse.
-enfant-m|Même chose.
+narrateur|Il fait un pas.
+narrateur|La maîtresse est sous le préau, maintenant.
+narrateur|Amir marche vers elle.
+narrateur|La pierre reste derrière.
+enfant-m|Encore trop près.
 narrateur|La maîtresse l'écoute encore.
 narrateur|Amir reste près d'elle.
 narrateur|Il pose une main sur le pilier du préau.
-narrateur|Le pilier est froid et un peu rugueux.
+narrateur|Le ciment est froid.
 enfant-m|Je reste ici.
-narrateur|Amir souffle.
-narrateur|Son cœur tape moins vite.
-narrateur|Le bateau de papier a arrêté de tourner.
+narrateur|Il souffle.
+narrateur|Le bateau a arrêté de tourner.
 narrateur|Papa vient le soir.
 narrateur|La pierre plate n'est plus chaude.
 narrateur|Amir la touche du bout du doigt.
 narrateur|Elle est juste tiède.
 papa|Tu as vu le bateau, encore ?
 enfant-m|Il ne tourne plus.
-enfant-m|Dans la cour, trop près.
-enfant-m|Puis sous le préau.
+enfant-m|Dans la flaque, trop près.
+enfant-m|Puis sur la pierre.
 enfant-m|J'ai dit stop.
 enfant-m|Je suis allé vers la maîtresse.
+papa|Près de l'eau ?
+enfant-m|Oui.
+papa|Et sous le préau ?
+enfant-m|Stop encore.
 papa|Bravo, Amir.
-papa|Tu as dit stop.
-papa|Tu t'es éloigné.
-papa|Tu as rejoint la maîtresse.
-papa|Même sous le préau ?
-enfant-m|Oui.
-papa|Même leçon, autre lieu.
+papa|Tu es allé près d'elle.
 enfant-m|Oui, papa.
 narrateur|Papa prend sa main.
 narrateur|Le bateau de papier reste dans l'herbe, tout mou.</t>
@@ -1489,14 +1506,14 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>slow</t>
         </is>
       </c>
       <c r="AA3" s="2" t="n">
         <v>0.9</v>
       </c>
       <c r="AB3" s="2" t="n">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
@@ -1596,12 +1613,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Amir a dit stop. Il s'est éloigné. Il a rejoint la maîtresse. Bravo. Dans la cour, et sous le préau. Stop, puis la maîtresse. Oui.</t>
+          <t>Amir a dit stop. Il a fait un pas. Il a rejoint la maîtresse. Bravo. Près de la flaque, et sous le préau. Stop, puis la maîtresse. Oui.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>Amir a dit stop. Il s'est éloigné. Il a rejoint la maîtresse. Bravo. Dans la cour, et sous le préau. Stop, puis la maîtresse. Oui.</t>
+          <t>Amir a dit stop. Il a fait un pas. Il a rejoint la maîtresse. Bravo. Près de la flaque, et sous le préau. Stop, puis la maîtresse. Oui.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1664,7 +1681,7 @@
         <v>0.96</v>
       </c>
       <c r="AB4" s="2" t="n">
-        <v>1.12</v>
+        <v>1.22</v>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
@@ -1741,10 +1758,10 @@
       <c r="AW4" t="inlineStr">
         <is>
           <t>narrateur|Amir a dit stop.
-narrateur|Il s'est éloigné.
+narrateur|Il a fait un pas.
 narrateur|Il a rejoint la maîtresse.
 papa|Bravo.
-papa|Dans la cour, et sous le préau.
+papa|Près de la flaque, et sous le préau.
 enfant-m|Stop, puis la maîtresse.
 papa|Oui.</t>
         </is>
@@ -1773,12 +1790,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Amir range son cartable. Je marche à côté. Oui, papa. On laisse le bateau dans l'herbe ? Oui. Il est trop mou, maintenant. Oui, papa. La flaque ne pousse plus rien. L'ombre du préau a grandi. La pierre est tiède, encore ? Juste un peu. Le pli du bateau reste ouvert.</t>
+          <t>Amir range son cartable. Je marche à côté. Oui, papa. On laisse le bateau dans l'herbe ? Oui. Il est trop mou, maintenant ? Oui, papa. La flaque ne pousse plus rien. L'ombre du préau a grandi. La pierre est tiède, encore ? Juste un peu. Le pli du bateau reste ouvert.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>Amir range son cartable. Je marche à côté. Oui, papa. On laisse le bateau dans l'herbe ? Oui. Il est trop mou, maintenant. Oui, papa. La flaque ne pousse plus rien. L'ombre du préau a grandi. La pierre est tiède, encore ? Juste un peu. Le pli du bateau reste ouvert.</t>
+          <t>Amir range son cartable. Je marche à côté. Oui, papa. On laisse le bateau dans l'herbe ? Oui. Il est trop mou, maintenant ? Oui, papa. La flaque ne pousse plus rien. L'ombre du préau a grandi. La pierre est tiède, encore ? Juste un peu. Le pli du bateau reste ouvert.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1841,7 +1858,7 @@
         <v>0.96</v>
       </c>
       <c r="AB5" s="2" t="n">
-        <v>1.12</v>
+        <v>1.22</v>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
@@ -1914,7 +1931,7 @@
 enfant-m|Oui, papa.
 papa|On laisse le bateau dans l'herbe ?
 enfant-m|Oui.
-papa|Il est trop mou, maintenant.
+papa|Il est trop mou, maintenant ?
 enfant-m|Oui, papa.
 narrateur|La flaque ne pousse plus rien.
 narrateur|L'ombre du préau a grandi.
@@ -1947,12 +1964,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>J'ai dit stop. Je suis allé vers la maîtresse. Bravo, Amir. Le bateau de papier sèche tout bas.</t>
+          <t>J'ai dit stop. Je suis allé vers la maîtresse. Bravo, Amir. Le bateau de papier sèche tout bas dans l'herbe.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>J'ai dit stop. Je suis allé vers la maîtresse. Bravo, Amir. Le bateau de papier sèche tout bas.</t>
+          <t>J'ai dit stop. Je suis allé vers la maîtresse. Bravo, Amir. Le bateau de papier sèche tout bas dans l'herbe.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2015,7 +2032,7 @@
         <v>0.92</v>
       </c>
       <c r="AB6" s="2" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
@@ -2090,7 +2107,7 @@
           <t>enfant-m|J'ai dit stop.
 enfant-m|Je suis allé vers la maîtresse.
 papa|Bravo, Amir.
-narrateur|Le bateau de papier sèche tout bas.</t>
+narrateur|Le bateau de papier sèche tout bas dans l'herbe.</t>
         </is>
       </c>
     </row>
@@ -2111,7 +2128,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A7"/>
+  <dimension ref="A1:A8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2161,6 +2178,13 @@
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
         <is>
           <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
